--- a/final/table/workbooks/SuppTable_S1_Population_structure_and_ancestry.xlsx
+++ b/final/table/workbooks/SuppTable_S1_Population_structure_and_ancestry.xlsx
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.918378222254973</v>
+        <v>0.91837822225492</v>
       </c>
       <c r="J2" t="s">
         <v>26</v>
@@ -640,7 +640,7 @@
         <v>8.72148319141142</v>
       </c>
       <c r="M2" t="n">
-        <v>8.67478278122236</v>
+        <v>8.67478278122237</v>
       </c>
       <c r="N2" t="n">
         <v>8.6826188653013</v>
@@ -826,7 +826,7 @@
         <v>5.57338377705515</v>
       </c>
       <c r="P5" t="n">
-        <v>4.97932058188861</v>
+        <v>4.9793205818886</v>
       </c>
       <c r="Q5" t="n">
         <v>5.26582219955623</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.942349669008028</v>
+        <v>0.942349669008072</v>
       </c>
       <c r="J7" t="s">
         <v>30</v>
@@ -941,7 +941,7 @@
         <v>0.00613978337359149</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00622473972435719</v>
+        <v>0.00622473972435718</v>
       </c>
       <c r="P7" t="n">
         <v>0.00633567265794079</v>
@@ -997,7 +997,7 @@
         <v>0.379407407827314</v>
       </c>
       <c r="N8" t="n">
-        <v>0.380152744529452</v>
+        <v>0.380152744529451</v>
       </c>
       <c r="O8" t="n">
         <v>0.365556237598569</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.918378222254973</v>
+        <v>0.91837822225492</v>
       </c>
       <c r="J9" t="s">
         <v>26</v>
@@ -1059,7 +1059,7 @@
         <v>0.0118118489388583</v>
       </c>
       <c r="O9" t="n">
-        <v>0.013096257236004</v>
+        <v>0.0130962572360039</v>
       </c>
       <c r="P9" t="n">
         <v>0.0120030524624752</v>
@@ -1150,16 +1150,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>2.73723687287213</v>
+        <v>2.7372368728719</v>
       </c>
       <c r="G11" t="n">
-        <v>0.740417597077736</v>
+        <v>0.740417597077771</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.942349669008028</v>
+        <v>0.942349669008072</v>
       </c>
       <c r="J11" t="s">
         <v>32</v>
@@ -1168,7 +1168,7 @@
         <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>11.8854211692332</v>
+        <v>11.8854211692333</v>
       </c>
       <c r="M11" t="n">
         <v>12.1636149567177</v>
@@ -1268,16 +1268,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>3.72003028179233</v>
+        <v>3.72003028179256</v>
       </c>
       <c r="G13" t="n">
-        <v>0.590386000021054</v>
+        <v>0.59038600002102</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.918378222254973</v>
+        <v>0.91837822225492</v>
       </c>
       <c r="J13" t="s">
         <v>30</v>
@@ -1289,7 +1289,7 @@
         <v>32.3128431615275</v>
       </c>
       <c r="M13" t="n">
-        <v>32.9518900439761</v>
+        <v>32.9518900439762</v>
       </c>
       <c r="N13" t="n">
         <v>33.2884051839146</v>
@@ -1354,7 +1354,7 @@
         <v>2.72807622728008</v>
       </c>
       <c r="O14" t="n">
-        <v>2.60244436679678</v>
+        <v>2.60244436679677</v>
       </c>
       <c r="P14" t="n">
         <v>2.73626987539736</v>
@@ -1404,10 +1404,10 @@
         <v>44</v>
       </c>
       <c r="L15" t="n">
-        <v>2.63871481436344</v>
+        <v>2.63871481436345</v>
       </c>
       <c r="M15" t="n">
-        <v>2.28696461436255</v>
+        <v>2.28696461436254</v>
       </c>
       <c r="N15" t="n">
         <v>2.17148886348999</v>
@@ -1534,7 +1534,7 @@
         <v>23.0887448305288</v>
       </c>
       <c r="P17" t="n">
-        <v>22.8349704718072</v>
+        <v>22.8349704718071</v>
       </c>
       <c r="Q17" t="n">
         <v>22.5991173460127</v>
@@ -1563,10 +1563,10 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>2.18715446364956</v>
+        <v>2.18715446364945</v>
       </c>
       <c r="G18" t="n">
-        <v>0.822689246378825</v>
+        <v>0.822689246378842</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1622,16 +1622,16 @@
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>3.56490428763573</v>
+        <v>3.56490428763561</v>
       </c>
       <c r="G19" t="n">
-        <v>0.613590344557406</v>
+        <v>0.613590344557423</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.859026482380369</v>
+        <v>0.859026482380392</v>
       </c>
       <c r="J19" t="s">
         <v>30</v>
@@ -1652,7 +1652,7 @@
         <v>6.06929512841397</v>
       </c>
       <c r="P19" t="n">
-        <v>6.68038533010051</v>
+        <v>6.6803853301005</v>
       </c>
       <c r="Q19" t="n">
         <v>6.09438088385546</v>
@@ -1817,7 +1817,7 @@
         <v>29</v>
       </c>
       <c r="L22" t="n">
-        <v>0.450746346597514</v>
+        <v>0.450746346597513</v>
       </c>
       <c r="M22" t="n">
         <v>0.439867900698595</v>
@@ -1829,7 +1829,7 @@
         <v>0.434369289099202</v>
       </c>
       <c r="P22" t="n">
-        <v>0.456340966511042</v>
+        <v>0.456340966511041</v>
       </c>
       <c r="Q22" t="n">
         <v>0.438992103157581</v>
@@ -1888,7 +1888,7 @@
         <v>0.0369559572295802</v>
       </c>
       <c r="P23" t="n">
-        <v>0.0366518548125264</v>
+        <v>0.0366518548125265</v>
       </c>
       <c r="Q23" t="n">
         <v>0.0388827965638499</v>
@@ -2035,13 +2035,13 @@
         <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>5.87108105866162</v>
+        <v>5.8710810586615</v>
       </c>
       <c r="G26" t="n">
-        <v>0.31896613275547</v>
+        <v>0.318966132755481</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00424917589591032</v>
+        <v>0.00424917589590977</v>
       </c>
       <c r="I26" t="n">
         <v>0.622259116961751</v>
@@ -2094,13 +2094,13 @@
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>8.4363261387756</v>
+        <v>8.43632613877583</v>
       </c>
       <c r="G27" t="n">
-        <v>0.133771927816055</v>
+        <v>0.133771927816044</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0167625665306127</v>
+        <v>0.0167625665306138</v>
       </c>
       <c r="I27" t="n">
         <v>0.547771425378957</v>
@@ -2239,7 +2239,7 @@
         <v>4.96490755750524</v>
       </c>
       <c r="O29" t="n">
-        <v>4.66903102399503</v>
+        <v>4.66903102399502</v>
       </c>
       <c r="P29" t="n">
         <v>4.51245018744337</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.849427422332016</v>
+        <v>0.849427422331975</v>
       </c>
       <c r="J30" t="s">
         <v>47</v>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.973313960483175</v>
+        <v>0.973313960483159</v>
       </c>
       <c r="J32" t="s">
         <v>51</v>
@@ -2566,13 +2566,13 @@
         <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>5.08112484036315</v>
+        <v>5.08112484036292</v>
       </c>
       <c r="G35" t="n">
-        <v>0.406060112376852</v>
+        <v>0.406060112376879</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00021292609019198</v>
+        <v>0.00021292609019138</v>
       </c>
       <c r="I35" t="n">
         <v>0.730838344475155</v>
@@ -2625,16 +2625,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>0.85615857205039</v>
+        <v>0.856158572050617</v>
       </c>
       <c r="G36" t="n">
-        <v>0.973313960483175</v>
+        <v>0.973313960483159</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.973313960483175</v>
+        <v>0.973313960483159</v>
       </c>
       <c r="J36" t="s">
         <v>52</v>
@@ -2652,7 +2652,7 @@
         <v>0.365190010382461</v>
       </c>
       <c r="S36" t="n">
-        <v>0.377161636591974</v>
+        <v>0.377161636591973</v>
       </c>
       <c r="T36" t="n">
         <v>0.379918870207017</v>
@@ -2661,7 +2661,7 @@
         <v>0.367936184367925</v>
       </c>
       <c r="V36" t="n">
-        <v>0.375954199803951</v>
+        <v>0.37595419980395</v>
       </c>
       <c r="W36" t="n">
         <v>0.376044910648238</v>
@@ -2802,16 +2802,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>2.81760581295998</v>
+        <v>2.81760581296021</v>
       </c>
       <c r="G39" t="n">
-        <v>0.728080647713156</v>
+        <v>0.728080647713121</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.849427422332016</v>
+        <v>0.849427422331975</v>
       </c>
       <c r="J39" t="s">
         <v>48</v>
@@ -2920,16 +2920,16 @@
         <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>3.81790306258085</v>
+        <v>3.81790306258108</v>
       </c>
       <c r="G41" t="n">
-        <v>0.575920049699867</v>
+        <v>0.575920049699833</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.806288069579813</v>
+        <v>0.806288069579766</v>
       </c>
       <c r="J41" t="s">
         <v>48</v>
@@ -2956,7 +2956,7 @@
         <v>32.4127419291234</v>
       </c>
       <c r="V41" t="n">
-        <v>33.636914461114</v>
+        <v>33.6369144611139</v>
       </c>
       <c r="W41" t="n">
         <v>32.7576412839944</v>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.806288069579813</v>
+        <v>0.806288069579766</v>
       </c>
       <c r="J42" t="s">
         <v>47</v>
@@ -3015,7 +3015,7 @@
         <v>2.61723600894495</v>
       </c>
       <c r="V42" t="n">
-        <v>2.73605423759247</v>
+        <v>2.73605423759248</v>
       </c>
       <c r="W42" t="n">
         <v>2.73253616557042</v>
@@ -3065,7 +3065,7 @@
         <v>2.61991805764566</v>
       </c>
       <c r="S43" t="n">
-        <v>2.44892731684433</v>
+        <v>2.44892731684432</v>
       </c>
       <c r="T43" t="n">
         <v>2.30217024157545</v>
@@ -3156,16 +3156,16 @@
         <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>4.8505408818055</v>
+        <v>4.85054088180573</v>
       </c>
       <c r="G45" t="n">
-        <v>0.434391529011376</v>
+        <v>0.434391529011347</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.506790117179939</v>
+        <v>0.506790117179905</v>
       </c>
       <c r="J45" t="s">
         <v>52</v>
@@ -3186,13 +3186,13 @@
         <v>23.0028036774751</v>
       </c>
       <c r="T45" t="n">
-        <v>24.1115978033773</v>
+        <v>24.1115978033772</v>
       </c>
       <c r="U45" t="n">
         <v>23.0125863766198</v>
       </c>
       <c r="V45" t="n">
-        <v>22.9513705533485</v>
+        <v>22.9513705533484</v>
       </c>
       <c r="W45" t="n">
         <v>23.3519196405749</v>
@@ -3301,7 +3301,7 @@
         <v>5.73466855410983</v>
       </c>
       <c r="S47" t="n">
-        <v>6.11333997745866</v>
+        <v>6.11333997745867</v>
       </c>
       <c r="T47" t="n">
         <v>6.27050231392748</v>
@@ -3310,7 +3310,7 @@
         <v>6.38332145940215</v>
       </c>
       <c r="V47" t="n">
-        <v>6.08866618549099</v>
+        <v>6.088666185491</v>
       </c>
       <c r="W47" t="n">
         <v>6.27528437708447</v>
@@ -3451,13 +3451,13 @@
         <v>6</v>
       </c>
       <c r="F50" t="n">
-        <v>7.81965974465993</v>
+        <v>7.8196597446597</v>
       </c>
       <c r="G50" t="n">
-        <v>0.166458596631718</v>
+        <v>0.166458596631731</v>
       </c>
       <c r="H50" t="n">
-        <v>0.00807925428269321</v>
+        <v>0.00807925428269256</v>
       </c>
       <c r="I50" t="n">
         <v>0.254956215845474</v>
@@ -3484,7 +3484,7 @@
         <v>0.44070928455045</v>
       </c>
       <c r="U50" t="n">
-        <v>0.447265528968808</v>
+        <v>0.447265528968807</v>
       </c>
       <c r="V50" t="n">
         <v>0.444688899281775</v>
@@ -3540,7 +3540,7 @@
         <v>0.0349968488320464</v>
       </c>
       <c r="T51" t="n">
-        <v>0.0454229381720932</v>
+        <v>0.0454229381720933</v>
       </c>
       <c r="U51" t="n">
         <v>0.0436014496540806</v>
@@ -3599,7 +3599,7 @@
         <v>13.9870195103059</v>
       </c>
       <c r="T52" t="n">
-        <v>13.5514057994318</v>
+        <v>13.5514057994319</v>
       </c>
       <c r="U52" t="n">
         <v>13.8142543095893</v>
@@ -3891,10 +3891,10 @@
         <v>4.49813932829266</v>
       </c>
       <c r="S57" t="n">
-        <v>4.42128464521915</v>
+        <v>4.42128464521916</v>
       </c>
       <c r="T57" t="n">
-        <v>4.84221320403911</v>
+        <v>4.84221320403912</v>
       </c>
       <c r="U57" t="n">
         <v>4.36100019095927</v>
@@ -4302,16 +4302,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>7.00151234239581</v>
+        <v>7.00151234239593</v>
       </c>
       <c r="G3" t="n">
-        <v>0.220527857413382</v>
+        <v>0.220527857413374</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00926626084442506</v>
+        <v>0.00926626084442559</v>
       </c>
       <c r="I3" t="n">
-        <v>0.441055714826765</v>
+        <v>0.441055714826748</v>
       </c>
     </row>
     <row r="4">
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.542185573099799</v>
+        <v>0.542185573099832</v>
       </c>
     </row>
     <row r="5">
@@ -4360,16 +4360,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>4.05037963643758</v>
+        <v>4.05037963643736</v>
       </c>
       <c r="G5" t="n">
-        <v>0.542185573099799</v>
+        <v>0.542185573099832</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.542185573099799</v>
+        <v>0.542185573099832</v>
       </c>
     </row>
     <row r="6">
